--- a/data/IPT_Tabel_B1.xlsx
+++ b/data/IPT_Tabel_B1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elise\Documents\Code_Projects\IPT_Work\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC060D56-74F1-4935-B7B4-DD68CC88AB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBBEB59-16AC-4677-A84F-64A6C8E21BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="852" yWindow="936" windowWidth="18984" windowHeight="11304" xr2:uid="{D946E7EC-82E9-46FF-B2BE-8435FC8A66C5}"/>
   </bookViews>
@@ -4715,9 +4715,6 @@
     <t>-115.90(g) </t>
   </si>
   <si>
-    <t>-563.46(g) </t>
-  </si>
-  <si>
     <r>
       <t>Fosfor (rood)</t>
     </r>
@@ -10673,6 +10670,9 @@
   </si>
   <si>
     <t>`-4163.1(l) -4194.8(g)`</t>
+  </si>
+  <si>
+    <t>`-563.46(g) </t>
   </si>
 </sst>
 </file>
@@ -11300,10 +11300,10 @@
         <v>23</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -11382,7 +11382,7 @@
         <v>44</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="M4" s="8" t="s">
         <v>45</v>
@@ -11464,7 +11464,7 @@
         <v>28</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>28</v>
@@ -11505,7 +11505,7 @@
         <v>28</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>64</v>
@@ -11587,10 +11587,10 @@
         <v>83</v>
       </c>
       <c r="L9" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>1184</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -11628,7 +11628,7 @@
         <v>28</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>91</v>
@@ -11669,7 +11669,7 @@
         <v>102</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="M11" s="7" t="s">
         <v>103</v>
@@ -11831,10 +11831,10 @@
         <v>141</v>
       </c>
       <c r="L15" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="M15" s="7" t="s">
         <v>1188</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="36" thickBot="1" x14ac:dyDescent="0.35">
@@ -12319,7 +12319,7 @@
         <v>28</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="M27" s="7" t="s">
         <v>28</v>
@@ -12520,10 +12520,10 @@
         <v>284</v>
       </c>
       <c r="L32" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="M32" s="7" t="s">
         <v>1191</v>
-      </c>
-      <c r="M32" s="7" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -12561,10 +12561,10 @@
         <v>295</v>
       </c>
       <c r="L33" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M33" s="7" t="s">
         <v>1193</v>
-      </c>
-      <c r="M33" s="7" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -12605,7 +12605,7 @@
         <v>305</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="36" thickBot="1" x14ac:dyDescent="0.35">
@@ -12725,10 +12725,10 @@
         <v>335</v>
       </c>
       <c r="L37" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="M37" s="7" t="s">
         <v>1196</v>
-      </c>
-      <c r="M37" s="7" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -12766,10 +12766,10 @@
         <v>313</v>
       </c>
       <c r="L38" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M38" s="7" t="s">
         <v>1198</v>
-      </c>
-      <c r="M38" s="7" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -12807,10 +12807,10 @@
         <v>352</v>
       </c>
       <c r="L39" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="M39" s="7" t="s">
         <v>1200</v>
-      </c>
-      <c r="M39" s="7" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -13053,10 +13053,10 @@
         <v>412</v>
       </c>
       <c r="L45" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="M45" s="7" t="s">
         <v>1202</v>
-      </c>
-      <c r="M45" s="7" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="34.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
@@ -13094,7 +13094,7 @@
         <v>422</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="M46" s="10" t="s">
         <v>423</v>
@@ -13135,7 +13135,7 @@
         <v>28</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="M47" s="7" t="s">
         <v>433</v>
@@ -13176,7 +13176,7 @@
         <v>442</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="M48" s="7" t="s">
         <v>443</v>
@@ -13217,10 +13217,10 @@
         <v>452</v>
       </c>
       <c r="L49" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="M49" s="7" t="s">
         <v>1207</v>
-      </c>
-      <c r="M49" s="7" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -13340,10 +13340,10 @@
         <v>482</v>
       </c>
       <c r="L52" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M52" s="7" t="s">
         <v>1209</v>
-      </c>
-      <c r="M52" s="7" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -13381,7 +13381,7 @@
         <v>492</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="M53" s="7" t="s">
         <v>493</v>
@@ -13425,45 +13425,45 @@
         <v>502</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>503</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="E55" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="F55" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="G55" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="H55" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L55" s="4" t="s">
         <v>510</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>511</v>
       </c>
       <c r="M55" s="10" t="s">
         <v>28</v>
@@ -13471,40 +13471,40 @@
     </row>
     <row r="56" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="E56" s="4" t="s">
+      <c r="F56" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="G56" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="H56" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="I56" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="I56" s="4" t="s">
+      <c r="J56" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L56" s="4" t="s">
         <v>518</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>519</v>
       </c>
       <c r="M56" s="10" t="s">
         <v>28</v>
@@ -13512,26 +13512,26 @@
     </row>
     <row r="57" spans="1:13" ht="46.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="G57" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>526</v>
-      </c>
       <c r="H57" s="2" t="s">
         <v>28</v>
       </c>
@@ -13545,7 +13545,7 @@
         <v>28</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="M57" s="7" t="s">
         <v>28</v>
@@ -13553,78 +13553,78 @@
     </row>
     <row r="58" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="E58" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="F58" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="H58" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="I58" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L58" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L58" s="4" t="s">
+      <c r="M58" s="10" t="s">
         <v>534</v>
-      </c>
-      <c r="M58" s="10" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="E59" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F59" s="4" t="s">
+      <c r="G59" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="H59" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="I59" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="I59" s="4" t="s">
+      <c r="J59" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="J59" s="4" t="s">
+      <c r="K59" s="4" t="s">
         <v>543</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>544</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>244</v>
@@ -13635,155 +13635,155 @@
     </row>
     <row r="60" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="H60" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="I60" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="I60" s="2" t="s">
+      <c r="J60" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="J60" s="2" t="s">
+      <c r="K60" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="K60" s="2" t="s">
-        <v>555</v>
-      </c>
       <c r="L60" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="M60" s="7" t="s">
         <v>1213</v>
-      </c>
-      <c r="M60" s="7" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="E61" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="F61" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="G61" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="H61" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="I61" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="I61" s="2" t="s">
+      <c r="J61" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="J61" s="2" t="s">
+      <c r="K61" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="K61" s="2" t="s">
-        <v>566</v>
-      </c>
       <c r="L61" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="M61" s="7" t="s">
         <v>1250</v>
-      </c>
-      <c r="M61" s="7" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="34.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D62" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="E62" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="F62" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="G62" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="H62" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="I62" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="I62" s="2" t="s">
+      <c r="J62" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="J62" s="2" t="s">
+      <c r="K62" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="L62" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="M62" s="7" t="s">
         <v>577</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="M62" s="7" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="E63" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="F63" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="H63" s="4" t="s">
+      <c r="I63" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="I63" s="4" t="s">
-        <v>587</v>
-      </c>
       <c r="J63" s="4" t="s">
         <v>28</v>
       </c>
@@ -13791,7 +13791,7 @@
         <v>28</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M63" s="10" t="s">
         <v>28</v>
@@ -13799,40 +13799,40 @@
     </row>
     <row r="64" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="D64" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="E64" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="F64" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L64" s="4" t="s">
         <v>592</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I64" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>593</v>
       </c>
       <c r="M64" s="10" t="s">
         <v>28</v>
@@ -13840,40 +13840,40 @@
     </row>
     <row r="65" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="D65" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="E65" s="4" t="s">
         <v>597</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="F65" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="G65" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L65" s="4" t="s">
         <v>599</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L65" s="4" t="s">
-        <v>600</v>
       </c>
       <c r="M65" s="10" t="s">
         <v>28</v>
@@ -13881,40 +13881,40 @@
     </row>
     <row r="66" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="D66" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="E66" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="F66" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L66" s="4" t="s">
         <v>605</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L66" s="4" t="s">
-        <v>606</v>
       </c>
       <c r="M66" s="10" t="s">
         <v>28</v>
@@ -13922,22 +13922,22 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="D67" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="E67" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="F67" s="4" t="s">
         <v>611</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>612</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>28</v>
@@ -13949,13 +13949,13 @@
         <v>28</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>28</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M67" s="10" t="s">
         <v>28</v>
@@ -13963,28 +13963,28 @@
     </row>
     <row r="68" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="D68" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="E68" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="F68" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="E68" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="F68" s="4" t="s">
+      <c r="G68" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="H68" s="4" t="s">
         <v>619</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>620</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>28</v>
@@ -13994,48 +13994,48 @@
       </c>
       <c r="K68" s="5"/>
       <c r="L68" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M68" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="D69" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="E69" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F69" s="2" t="s">
+      <c r="G69" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="H69" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J69" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="H69" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J69" s="2" t="s">
+      <c r="K69" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="K69" s="2" t="s">
-        <v>629</v>
-      </c>
       <c r="L69" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="M69" s="7" t="s">
         <v>28</v>
@@ -14043,114 +14043,114 @@
     </row>
     <row r="70" spans="1:13" ht="34.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D70" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="F70" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="G70" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="H70" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="H70" s="2" t="s">
+      <c r="I70" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="I70" s="2" t="s">
+      <c r="J70" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="J70" s="2" t="s">
+      <c r="K70" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="K70" s="2" t="s">
-        <v>640</v>
-      </c>
       <c r="L70" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="M70" s="7" t="s">
         <v>1217</v>
-      </c>
-      <c r="M70" s="7" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="D71" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="E71" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="E71" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F71" s="4" t="s">
+      <c r="G71" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="H71" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="H71" s="4" t="s">
+      <c r="I71" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="I71" s="4" t="s">
+      <c r="J71" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="J71" s="4" t="s">
+      <c r="K71" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="K71" s="4" t="s">
+      <c r="L71" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="L71" s="4" t="s">
+      <c r="M71" s="10" t="s">
         <v>651</v>
-      </c>
-      <c r="M71" s="10" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="E72" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="F72" s="4" t="s">
         <v>657</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="G72" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="H72" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="H72" s="4" t="s">
+      <c r="I72" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="I72" s="4" t="s">
-        <v>661</v>
-      </c>
       <c r="J72" s="4" t="s">
         <v>28</v>
       </c>
@@ -14158,7 +14158,7 @@
         <v>28</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M72" s="10" t="s">
         <v>28</v>
@@ -14166,20 +14166,20 @@
     </row>
     <row r="73" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="D73" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>666</v>
-      </c>
       <c r="F73" s="2" t="s">
         <v>28</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>28</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="M73" s="7" t="s">
         <v>28</v>
@@ -14207,29 +14207,29 @@
     </row>
     <row r="74" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="E74" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="F74" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="G74" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="G74" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>673</v>
-      </c>
       <c r="I74" s="4" t="s">
         <v>28</v>
       </c>
@@ -14240,7 +14240,7 @@
         <v>28</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M74" s="10" t="s">
         <v>28</v>
@@ -14248,32 +14248,32 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="D75" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="E75" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="F75" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="G75" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="H75" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="H75" s="4" t="s">
+      <c r="I75" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="I75" s="4" t="s">
-        <v>682</v>
-      </c>
       <c r="J75" s="4" t="s">
         <v>28</v>
       </c>
@@ -14281,7 +14281,7 @@
         <v>28</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M75" s="10" t="s">
         <v>28</v>
@@ -14289,40 +14289,40 @@
     </row>
     <row r="76" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>683</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="D76" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="E76" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="F76" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="G76" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H76" s="4" t="s">
+      <c r="I76" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="I76" s="4" t="s">
+      <c r="J76" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L76" s="4" t="s">
         <v>691</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K76" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>692</v>
       </c>
       <c r="M76" s="10" t="s">
         <v>28</v>
@@ -14330,32 +14330,32 @@
     </row>
     <row r="77" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="C77" s="3" t="s">
+      <c r="D77" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="E77" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="F77" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="G77" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="H77" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="H77" s="4" t="s">
+      <c r="I77" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="I77" s="4" t="s">
-        <v>700</v>
-      </c>
       <c r="J77" s="4" t="s">
         <v>28</v>
       </c>
@@ -14363,7 +14363,7 @@
         <v>28</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M77" s="10" t="s">
         <v>28</v>
@@ -14371,40 +14371,40 @@
     </row>
     <row r="78" spans="1:13" ht="36" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="E78" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="F78" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="G78" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="H78" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="H78" s="4" t="s">
+      <c r="I78" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="I78" s="4" t="s">
+      <c r="J78" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L78" s="4" t="s">
         <v>709</v>
-      </c>
-      <c r="J78" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K78" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L78" s="4" t="s">
-        <v>710</v>
       </c>
       <c r="M78" s="10" t="s">
         <v>28</v>
@@ -14412,19 +14412,19 @@
     </row>
     <row r="79" spans="1:13" ht="47.4" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="E79" s="4" t="s">
         <v>714</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>715</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>28</v>
@@ -14453,40 +14453,40 @@
     </row>
     <row r="80" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="D80" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="E80" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="F80" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="G80" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="H80" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L80" s="4" t="s">
         <v>722</v>
-      </c>
-      <c r="H80" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="I80" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J80" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K80" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L80" s="4" t="s">
-        <v>723</v>
       </c>
       <c r="M80" s="10" t="s">
         <v>28</v>
@@ -14494,104 +14494,104 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="E81" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="E81" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F81" s="4" t="s">
+      <c r="G81" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="H81" s="4" t="s">
+      <c r="I81" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="I81" s="4" t="s">
+      <c r="J81" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="J81" s="4" t="s">
+      <c r="K81" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="K81" s="4" t="s">
+      <c r="L81" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="L81" s="4" t="s">
+      <c r="M81" s="10" t="s">
         <v>734</v>
-      </c>
-      <c r="M81" s="10" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="D82" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="E82" s="2" t="s">
         <v>739</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>740</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G82" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="H82" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="H82" s="2" t="s">
+      <c r="I82" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="I82" s="2" t="s">
+      <c r="J82" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="J82" s="2" t="s">
+      <c r="K82" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="K82" s="2" t="s">
-        <v>745</v>
-      </c>
       <c r="L82" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="M82" s="7" t="s">
         <v>1220</v>
-      </c>
-      <c r="M82" s="7" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="E83" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="E83" s="4" t="s">
+      <c r="F83" s="4" t="s">
         <v>750</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>751</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>28</v>
@@ -14603,106 +14603,106 @@
         <v>28</v>
       </c>
       <c r="J83" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="K83" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="K83" s="4" t="s">
+      <c r="L83" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="L83" s="4" t="s">
+      <c r="M83" s="10" t="s">
         <v>754</v>
-      </c>
-      <c r="M83" s="10" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="D84" s="4" t="s">
         <v>758</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="E84" s="4" t="s">
         <v>759</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="F84" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="G84" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H84" s="4" t="s">
         <v>761</v>
       </c>
-      <c r="G84" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H84" s="4" t="s">
+      <c r="I84" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J84" s="4" t="s">
         <v>762</v>
       </c>
-      <c r="I84" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J84" s="4" t="s">
+      <c r="K84" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="K84" s="4" t="s">
+      <c r="L84" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="L84" s="4" t="s">
+      <c r="M84" s="10" t="s">
         <v>765</v>
-      </c>
-      <c r="M84" s="10" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="D85" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="E85" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="E85" s="2" t="s">
+      <c r="F85" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="F85" s="2" t="s">
+      <c r="G85" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H85" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="G85" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H85" s="2" t="s">
+      <c r="I85" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J85" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="I85" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J85" s="2" t="s">
+      <c r="K85" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="K85" s="2" t="s">
-        <v>775</v>
-      </c>
       <c r="L85" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="M85" s="7" t="s">
         <v>1222</v>
-      </c>
-      <c r="M85" s="7" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>776</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>777</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>134</v>
@@ -14714,189 +14714,189 @@
         <v>28</v>
       </c>
       <c r="F86" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="G86" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="H86" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="H86" s="2" t="s">
+      <c r="I86" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="I86" s="2" t="s">
+      <c r="J86" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="J86" s="2" t="s">
+      <c r="K86" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="K86" s="2" t="s">
-        <v>783</v>
-      </c>
       <c r="L86" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="M86" s="7" t="s">
         <v>1224</v>
-      </c>
-      <c r="M86" s="7" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="34.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="E87" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="F87" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="G87" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="H87" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="H87" s="2" t="s">
+      <c r="I87" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="M87" s="7" t="s">
         <v>791</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="J87" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K87" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>1226</v>
-      </c>
-      <c r="M87" s="7" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="D88" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="F88" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="H88" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="H88" s="2" t="s">
+      <c r="I88" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="I88" s="2" t="s">
+      <c r="J88" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="J88" s="2" t="s">
+      <c r="K88" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="K88" s="2" t="s">
-        <v>803</v>
-      </c>
       <c r="L88" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="M88" s="7" t="s">
         <v>1227</v>
-      </c>
-      <c r="M88" s="7" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="9" t="s">
+        <v>803</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="D89" s="4" t="s">
         <v>806</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="E89" s="4" t="s">
         <v>807</v>
       </c>
-      <c r="E89" s="4" t="s">
+      <c r="F89" s="4" t="s">
         <v>808</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="G89" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H89" s="4" t="s">
         <v>809</v>
       </c>
-      <c r="G89" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H89" s="4" t="s">
+      <c r="I89" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M89" s="10" t="s">
         <v>810</v>
-      </c>
-      <c r="I89" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J89" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K89" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L89" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M89" s="10" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A90" s="9" t="s">
+        <v>811</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="D90" s="4" t="s">
         <v>814</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="E90" s="4" t="s">
         <v>815</v>
       </c>
-      <c r="E90" s="4" t="s">
+      <c r="F90" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L90" s="4" t="s">
         <v>816</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I90" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J90" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K90" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L90" s="4" t="s">
-        <v>817</v>
       </c>
       <c r="M90" s="10" t="s">
         <v>28</v>
@@ -14904,40 +14904,40 @@
     </row>
     <row r="91" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="C91" s="3" t="s">
         <v>819</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="D91" s="4" t="s">
         <v>820</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="E91" s="4" t="s">
         <v>821</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="F91" s="4" t="s">
         <v>822</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="G91" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="H91" s="4" t="s">
         <v>824</v>
       </c>
-      <c r="H91" s="4" t="s">
+      <c r="I91" s="4" t="s">
         <v>825</v>
       </c>
-      <c r="I91" s="4" t="s">
+      <c r="J91" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L91" s="4" t="s">
         <v>826</v>
-      </c>
-      <c r="J91" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K91" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L91" s="4" t="s">
-        <v>827</v>
       </c>
       <c r="M91" s="10" t="s">
         <v>28</v>
@@ -14945,40 +14945,40 @@
     </row>
     <row r="92" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="9" t="s">
+        <v>827</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>829</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="D92" s="4" t="s">
         <v>830</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="E92" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F92" s="4" t="s">
         <v>831</v>
       </c>
-      <c r="E92" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F92" s="4" t="s">
+      <c r="G92" s="4" t="s">
         <v>832</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="H92" s="4" t="s">
         <v>833</v>
       </c>
-      <c r="H92" s="4" t="s">
+      <c r="I92" s="4" t="s">
         <v>834</v>
       </c>
-      <c r="I92" s="4" t="s">
+      <c r="J92" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L92" s="4" t="s">
         <v>835</v>
-      </c>
-      <c r="J92" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K92" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L92" s="4" t="s">
-        <v>836</v>
       </c>
       <c r="M92" s="10" t="s">
         <v>28</v>
@@ -14986,29 +14986,29 @@
     </row>
     <row r="93" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D93" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="E93" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="F93" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="F93" s="2" t="s">
+      <c r="G93" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="G93" s="2" t="s">
+      <c r="H93" s="2" t="s">
         <v>843</v>
       </c>
-      <c r="H93" s="2" t="s">
-        <v>844</v>
-      </c>
       <c r="I93" s="2" t="s">
         <v>28</v>
       </c>
@@ -15019,7 +15019,7 @@
         <v>28</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="M93" s="7" t="s">
         <v>28</v>
@@ -15027,40 +15027,40 @@
     </row>
     <row r="94" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="D94" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="E94" s="4" t="s">
         <v>848</v>
       </c>
-      <c r="E94" s="4" t="s">
+      <c r="F94" s="4" t="s">
         <v>849</v>
       </c>
-      <c r="F94" s="4" t="s">
+      <c r="G94" s="4" t="s">
         <v>850</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="H94" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L94" s="4" t="s">
         <v>851</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J94" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L94" s="4" t="s">
-        <v>852</v>
       </c>
       <c r="M94" s="10" t="s">
         <v>28</v>
@@ -15068,40 +15068,40 @@
     </row>
     <row r="95" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A95" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="C95" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="D95" s="4" t="s">
         <v>855</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="E95" s="4" t="s">
         <v>856</v>
       </c>
-      <c r="E95" s="4" t="s">
+      <c r="F95" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="F95" s="4" t="s">
+      <c r="G95" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L95" s="4" t="s">
         <v>858</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I95" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J95" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K95" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L95" s="4" t="s">
-        <v>859</v>
       </c>
       <c r="M95" s="10" t="s">
         <v>28</v>
@@ -15109,40 +15109,40 @@
     </row>
     <row r="96" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A96" s="9" t="s">
+        <v>859</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="D96" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="E96" s="4" t="s">
         <v>863</v>
       </c>
-      <c r="E96" s="4" t="s">
+      <c r="F96" s="4" t="s">
         <v>864</v>
       </c>
-      <c r="F96" s="4" t="s">
+      <c r="G96" s="4" t="s">
         <v>865</v>
       </c>
-      <c r="G96" s="4" t="s">
+      <c r="H96" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L96" s="4" t="s">
         <v>866</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I96" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J96" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K96" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L96" s="4" t="s">
-        <v>867</v>
       </c>
       <c r="M96" s="10" t="s">
         <v>28</v>
@@ -15150,22 +15150,22 @@
     </row>
     <row r="97" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A97" s="9" t="s">
+        <v>867</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>869</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="D97" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="E97" s="4" t="s">
         <v>871</v>
       </c>
-      <c r="E97" s="4" t="s">
+      <c r="F97" s="4" t="s">
         <v>872</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>873</v>
       </c>
       <c r="G97" s="4" t="s">
         <v>279</v>
@@ -15183,7 +15183,7 @@
         <v>28</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="M97" s="10" t="s">
         <v>28</v>
@@ -15191,40 +15191,40 @@
     </row>
     <row r="98" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A98" s="9" t="s">
+        <v>874</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>875</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="D98" s="4" t="s">
         <v>877</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="E98" s="4" t="s">
         <v>878</v>
       </c>
-      <c r="E98" s="4" t="s">
+      <c r="F98" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L98" s="4" t="s">
         <v>879</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I98" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J98" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K98" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L98" s="4" t="s">
-        <v>880</v>
       </c>
       <c r="M98" s="10" t="s">
         <v>28</v>
@@ -15232,40 +15232,40 @@
     </row>
     <row r="99" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
+        <v>880</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>881</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="C99" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="D99" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="E99" s="4" t="s">
         <v>884</v>
       </c>
-      <c r="E99" s="4" t="s">
+      <c r="F99" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L99" s="4" t="s">
         <v>885</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I99" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J99" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K99" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L99" s="4" t="s">
-        <v>886</v>
       </c>
       <c r="M99" s="10" t="s">
         <v>28</v>
@@ -15273,40 +15273,40 @@
     </row>
     <row r="100" spans="1:13" ht="36" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
+        <v>886</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="C100" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="D100" s="4" t="s">
         <v>889</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="E100" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L100" s="4" t="s">
         <v>890</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I100" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J100" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K100" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L100" s="4" t="s">
-        <v>891</v>
       </c>
       <c r="M100" s="10" t="s">
         <v>28</v>
@@ -15314,40 +15314,40 @@
     </row>
     <row r="101" spans="1:13" ht="36" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>892</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="C101" s="3" t="s">
         <v>893</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="D101" s="4" t="s">
         <v>894</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="E101" s="4" t="s">
         <v>895</v>
       </c>
-      <c r="E101" s="4" t="s">
+      <c r="F101" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L101" s="4" t="s">
         <v>896</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I101" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J101" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K101" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L101" s="4" t="s">
-        <v>897</v>
       </c>
       <c r="M101" s="10" t="s">
         <v>28</v>
@@ -15355,28 +15355,28 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="C102" s="3" t="s">
         <v>899</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="D102" s="4" t="s">
         <v>900</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="E102" s="4" t="s">
         <v>901</v>
       </c>
-      <c r="E102" s="4" t="s">
+      <c r="F102" s="4" t="s">
         <v>902</v>
       </c>
-      <c r="F102" s="4" t="s">
-        <v>903</v>
-      </c>
       <c r="G102" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>28</v>
@@ -15388,7 +15388,7 @@
         <v>28</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M102" s="10" t="s">
         <v>28</v>
@@ -15396,92 +15396,92 @@
     </row>
     <row r="103" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="9" t="s">
+        <v>903</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>904</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="C103" s="3" t="s">
         <v>905</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="D103" s="4" t="s">
         <v>906</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="E103" s="4" t="s">
         <v>907</v>
       </c>
-      <c r="E103" s="4" t="s">
+      <c r="F103" s="4" t="s">
         <v>908</v>
       </c>
-      <c r="F103" s="4" t="s">
+      <c r="G103" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H103" s="4" t="s">
         <v>909</v>
       </c>
-      <c r="G103" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H103" s="4" t="s">
+      <c r="I103" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L103" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M103" s="10" t="s">
         <v>910</v>
-      </c>
-      <c r="I103" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J103" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K103" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L103" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M103" s="10" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>912</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="C104" s="3" t="s">
         <v>913</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="D104" s="4" t="s">
         <v>914</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="E104" s="4" t="s">
         <v>915</v>
       </c>
-      <c r="E104" s="4" t="s">
+      <c r="F104" s="4" t="s">
         <v>916</v>
       </c>
-      <c r="F104" s="4" t="s">
+      <c r="G104" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H104" s="4" t="s">
         <v>917</v>
       </c>
-      <c r="G104" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H104" s="4" t="s">
+      <c r="I104" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J104" s="4" t="s">
         <v>918</v>
       </c>
-      <c r="I104" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J104" s="4" t="s">
+      <c r="K104" s="4" t="s">
         <v>919</v>
       </c>
-      <c r="K104" s="4" t="s">
+      <c r="L104" s="4" t="s">
         <v>920</v>
       </c>
-      <c r="L104" s="4" t="s">
+      <c r="M104" s="10" t="s">
         <v>921</v>
-      </c>
-      <c r="M104" s="10" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="6" t="s">
+        <v>922</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>923</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>924</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>476</v>
@@ -15490,121 +15490,121 @@
         <v>477</v>
       </c>
       <c r="E105" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="F105" s="2" t="s">
         <v>925</v>
       </c>
-      <c r="F105" s="2" t="s">
+      <c r="G105" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H105" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="G105" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H105" s="2" t="s">
+      <c r="I105" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J105" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="I105" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J105" s="2" t="s">
+      <c r="K105" s="2" t="s">
         <v>928</v>
       </c>
-      <c r="K105" s="2" t="s">
-        <v>929</v>
-      </c>
       <c r="L105" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M105" s="7" t="s">
         <v>1230</v>
-      </c>
-      <c r="M105" s="7" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="9" t="s">
+        <v>929</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="C106" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="D106" s="4" t="s">
         <v>932</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="E106" s="4" t="s">
         <v>933</v>
       </c>
-      <c r="E106" s="4" t="s">
+      <c r="F106" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K106" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L106" s="4" t="s">
         <v>934</v>
       </c>
-      <c r="F106" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I106" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J106" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K106" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L106" s="4" t="s">
+      <c r="M106" s="10" t="s">
         <v>935</v>
-      </c>
-      <c r="M106" s="10" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="E107" s="2" t="s">
+      <c r="F107" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="F107" s="2" t="s">
+      <c r="G107" s="2" t="s">
         <v>940</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>941</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>350</v>
       </c>
       <c r="I107" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="J107" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="J107" s="2" t="s">
+      <c r="K107" s="2" t="s">
         <v>943</v>
       </c>
-      <c r="K107" s="2" t="s">
-        <v>944</v>
-      </c>
       <c r="L107" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="M107" s="7" t="s">
         <v>1232</v>
-      </c>
-      <c r="M107" s="7" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>945</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>946</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>287</v>
@@ -15613,225 +15613,225 @@
         <v>288</v>
       </c>
       <c r="E108" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="F108" s="4" t="s">
         <v>947</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="G108" s="4" t="s">
         <v>948</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="H108" s="4" t="s">
         <v>949</v>
       </c>
-      <c r="H108" s="4" t="s">
+      <c r="I108" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J108" s="4" t="s">
         <v>950</v>
       </c>
-      <c r="I108" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J108" s="4" t="s">
+      <c r="K108" s="4" t="s">
         <v>951</v>
       </c>
-      <c r="K108" s="4" t="s">
+      <c r="L108" s="4" t="s">
         <v>952</v>
       </c>
-      <c r="L108" s="4" t="s">
+      <c r="M108" s="10" t="s">
         <v>953</v>
-      </c>
-      <c r="M108" s="10" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="6" t="s">
+        <v>954</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="2" t="s">
         <v>957</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="E109" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F109" s="2" t="s">
         <v>958</v>
       </c>
-      <c r="E109" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F109" s="2" t="s">
+      <c r="G109" s="2" t="s">
         <v>959</v>
       </c>
-      <c r="G109" s="2" t="s">
+      <c r="H109" s="2" t="s">
         <v>960</v>
       </c>
-      <c r="H109" s="2" t="s">
+      <c r="I109" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="I109" s="2" t="s">
+      <c r="J109" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="J109" s="2" t="s">
+      <c r="K109" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="K109" s="2" t="s">
-        <v>964</v>
-      </c>
       <c r="L109" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="M109" s="7" t="s">
         <v>1234</v>
-      </c>
-      <c r="M109" s="7" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="6" t="s">
+        <v>964</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>965</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="D110" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="E110" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="F110" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="F110" s="2" t="s">
+      <c r="G110" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H110" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="G110" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H110" s="2" t="s">
+      <c r="I110" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J110" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="I110" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J110" s="2" t="s">
+      <c r="K110" s="2" t="s">
         <v>972</v>
       </c>
-      <c r="K110" s="2" t="s">
-        <v>973</v>
-      </c>
       <c r="L110" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="M110" s="7" t="s">
         <v>1236</v>
-      </c>
-      <c r="M110" s="7" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="9" t="s">
+        <v>973</v>
+      </c>
+      <c r="B111" s="3" t="s">
         <v>974</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="C111" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="E111" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>967</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>968</v>
-      </c>
-      <c r="E111" s="4" t="s">
+      <c r="F111" s="4" t="s">
         <v>976</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="G111" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H111" s="4" t="s">
         <v>977</v>
       </c>
-      <c r="G111" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H111" s="4" t="s">
+      <c r="I111" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J111" s="4" t="s">
         <v>978</v>
       </c>
-      <c r="I111" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J111" s="4" t="s">
+      <c r="K111" s="4" t="s">
         <v>979</v>
       </c>
-      <c r="K111" s="4" t="s">
+      <c r="L111" s="4" t="s">
         <v>980</v>
       </c>
-      <c r="L111" s="4" t="s">
+      <c r="M111" s="10" t="s">
         <v>981</v>
-      </c>
-      <c r="M111" s="10" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A112" s="9" t="s">
+        <v>982</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>983</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="C112" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="D112" s="4" t="s">
         <v>985</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="E112" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F112" s="4" t="s">
         <v>986</v>
       </c>
-      <c r="E112" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F112" s="4" t="s">
+      <c r="G112" s="4" t="s">
         <v>987</v>
       </c>
-      <c r="G112" s="4" t="s">
+      <c r="H112" s="4" t="s">
         <v>988</v>
       </c>
-      <c r="H112" s="4" t="s">
+      <c r="I112" s="4" t="s">
         <v>989</v>
       </c>
-      <c r="I112" s="4" t="s">
+      <c r="J112" s="4" t="s">
         <v>990</v>
       </c>
-      <c r="J112" s="4" t="s">
+      <c r="K112" s="4" t="s">
         <v>991</v>
       </c>
-      <c r="K112" s="4" t="s">
+      <c r="L112" s="4" t="s">
         <v>992</v>
       </c>
-      <c r="L112" s="4" t="s">
+      <c r="M112" s="10" t="s">
         <v>993</v>
-      </c>
-      <c r="M112" s="10" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="34.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="6" t="s">
+        <v>994</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="E113" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="F113" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="F113" s="2" t="s">
+      <c r="G113" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="G113" s="2" t="s">
+      <c r="H113" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="H113" s="2" t="s">
+      <c r="I113" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="I113" s="2" t="s">
-        <v>1003</v>
-      </c>
       <c r="J113" s="2" t="s">
         <v>28</v>
       </c>
@@ -15839,7 +15839,7 @@
         <v>28</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="M113" s="7" t="s">
         <v>28</v>
@@ -15847,40 +15847,40 @@
     </row>
     <row r="114" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="9" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>1004</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="C114" s="3" t="s">
         <v>1005</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="D114" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="E114" s="4" t="s">
         <v>1006</v>
       </c>
-      <c r="D114" s="4" t="s">
-        <v>968</v>
-      </c>
-      <c r="E114" s="4" t="s">
+      <c r="F114" s="4" t="s">
         <v>1007</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="G114" s="4" t="s">
         <v>1008</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="H114" s="4" t="s">
         <v>1009</v>
       </c>
-      <c r="H114" s="4" t="s">
+      <c r="I114" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K114" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L114" s="4" t="s">
         <v>1010</v>
-      </c>
-      <c r="I114" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J114" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K114" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L114" s="4" t="s">
-        <v>1011</v>
       </c>
       <c r="M114" s="10" t="s">
         <v>28</v>
@@ -15888,37 +15888,37 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="9" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B115" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="C115" s="3" t="s">
         <v>1013</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="D115" s="4" t="s">
         <v>1014</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="E115" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F115" s="4" t="s">
         <v>1015</v>
       </c>
-      <c r="E115" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F115" s="4" t="s">
+      <c r="G115" s="4" t="s">
         <v>1016</v>
       </c>
-      <c r="G115" s="4" t="s">
+      <c r="H115" s="4" t="s">
         <v>1017</v>
       </c>
-      <c r="H115" s="4" t="s">
+      <c r="I115" s="4" t="s">
         <v>1018</v>
       </c>
-      <c r="I115" s="4" t="s">
+      <c r="J115" s="4" t="s">
         <v>1019</v>
       </c>
-      <c r="J115" s="4" t="s">
+      <c r="K115" s="4" t="s">
         <v>1020</v>
-      </c>
-      <c r="K115" s="4" t="s">
-        <v>1021</v>
       </c>
       <c r="L115" s="4" t="s">
         <v>244</v>
@@ -15929,40 +15929,40 @@
     </row>
     <row r="116" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A116" s="9" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B116" s="3" t="s">
         <v>1022</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="C116" s="3" t="s">
         <v>1023</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="D116" s="4" t="s">
         <v>1024</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="E116" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F116" s="4" t="s">
         <v>1025</v>
       </c>
-      <c r="E116" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F116" s="4" t="s">
+      <c r="G116" s="4" t="s">
         <v>1026</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="H116" s="4" t="s">
         <v>1027</v>
       </c>
-      <c r="H116" s="4" t="s">
+      <c r="I116" s="4" t="s">
         <v>1028</v>
-      </c>
-      <c r="I116" s="4" t="s">
-        <v>1029</v>
       </c>
       <c r="J116" s="4" t="s">
         <v>376</v>
       </c>
       <c r="K116" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="L116" s="4" t="s">
         <v>1030</v>
-      </c>
-      <c r="L116" s="4" t="s">
-        <v>1031</v>
       </c>
       <c r="M116" s="10" t="s">
         <v>28</v>
@@ -15970,40 +15970,40 @@
     </row>
     <row r="117" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A117" s="9" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B117" s="3" t="s">
         <v>1032</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="C117" s="3" t="s">
         <v>1033</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="D117" s="4" t="s">
         <v>1034</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="E117" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F117" s="4" t="s">
         <v>1035</v>
       </c>
-      <c r="E117" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F117" s="4" t="s">
+      <c r="G117" s="4" t="s">
         <v>1036</v>
       </c>
-      <c r="G117" s="4" t="s">
+      <c r="H117" s="4" t="s">
         <v>1037</v>
       </c>
-      <c r="H117" s="4" t="s">
+      <c r="I117" s="4" t="s">
         <v>1038</v>
       </c>
-      <c r="I117" s="4" t="s">
+      <c r="J117" s="4" t="s">
         <v>1039</v>
       </c>
-      <c r="J117" s="4" t="s">
+      <c r="K117" s="4" t="s">
         <v>1040</v>
       </c>
-      <c r="K117" s="4" t="s">
+      <c r="L117" s="4" t="s">
         <v>1041</v>
-      </c>
-      <c r="L117" s="4" t="s">
-        <v>1042</v>
       </c>
       <c r="M117" s="10" t="s">
         <v>28</v>
@@ -16011,122 +16011,122 @@
     </row>
     <row r="118" spans="1:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D118" s="2" t="s">
         <v>1044</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D118" s="2" t="s">
+      <c r="E118" s="2" t="s">
         <v>1045</v>
       </c>
-      <c r="E118" s="2" t="s">
+      <c r="F118" s="2" t="s">
         <v>1046</v>
       </c>
-      <c r="F118" s="2" t="s">
+      <c r="G118" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H118" s="2" t="s">
         <v>1047</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>1048</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>367</v>
       </c>
       <c r="J118" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="K118" s="2" t="s">
         <v>1049</v>
       </c>
-      <c r="K118" s="2" t="s">
-        <v>1050</v>
-      </c>
       <c r="L118" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="M118" s="7" t="s">
         <v>1239</v>
-      </c>
-      <c r="M118" s="7" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="E119" s="2" t="s">
         <v>1054</v>
       </c>
-      <c r="E119" s="2" t="s">
+      <c r="F119" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="F119" s="2" t="s">
+      <c r="G119" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="G119" s="2" t="s">
+      <c r="H119" s="2" t="s">
         <v>1057</v>
       </c>
-      <c r="H119" s="2" t="s">
+      <c r="I119" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="I119" s="2" t="s">
+      <c r="J119" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="J119" s="2" t="s">
+      <c r="K119" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="K119" s="2" t="s">
-        <v>1061</v>
-      </c>
       <c r="L119" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="M119" s="7" t="s">
         <v>1242</v>
-      </c>
-      <c r="M119" s="7" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="6" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="E120" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="E120" s="2" t="s">
+      <c r="F120" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="F120" s="2" t="s">
+      <c r="G120" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="G120" s="2" t="s">
+      <c r="H120" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="H120" s="2" t="s">
+      <c r="I120" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="I120" s="2" t="s">
+      <c r="J120" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="J120" s="2" t="s">
+      <c r="K120" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="K120" s="2" t="s">
-        <v>1071</v>
-      </c>
       <c r="L120" s="2" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="M120" s="7" t="s">
         <v>28</v>
@@ -16134,81 +16134,81 @@
     </row>
     <row r="121" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="9" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B121" s="3" t="s">
         <v>1072</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="C121" s="3" t="s">
         <v>1073</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="D121" s="4" t="s">
         <v>1074</v>
       </c>
-      <c r="D121" s="4" t="s">
+      <c r="E121" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F121" s="4" t="s">
         <v>1075</v>
       </c>
-      <c r="E121" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F121" s="4" t="s">
+      <c r="G121" s="4" t="s">
         <v>1076</v>
       </c>
-      <c r="G121" s="4" t="s">
+      <c r="H121" s="4" t="s">
         <v>1077</v>
       </c>
-      <c r="H121" s="4" t="s">
+      <c r="I121" s="4" t="s">
         <v>1078</v>
       </c>
-      <c r="I121" s="4" t="s">
+      <c r="J121" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="K121" s="4" t="s">
         <v>1079</v>
-      </c>
-      <c r="J121" s="4" t="s">
-        <v>944</v>
-      </c>
-      <c r="K121" s="4" t="s">
-        <v>1080</v>
       </c>
       <c r="L121" s="4" t="s">
         <v>244</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A122" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>1082</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="C122" s="3" t="s">
         <v>1083</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="D122" s="4" t="s">
         <v>1084</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="E122" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F122" s="4" t="s">
         <v>1085</v>
       </c>
-      <c r="E122" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F122" s="4" t="s">
+      <c r="G122" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H122" s="4" t="s">
         <v>1086</v>
       </c>
-      <c r="G122" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H122" s="4" t="s">
+      <c r="I122" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J122" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K122" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L122" s="4" t="s">
         <v>1087</v>
-      </c>
-      <c r="I122" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J122" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K122" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L122" s="4" t="s">
-        <v>1088</v>
       </c>
       <c r="M122" s="10" t="s">
         <v>28</v>
@@ -16216,40 +16216,40 @@
     </row>
     <row r="123" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="6" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C123" s="1" t="s">
+      <c r="D123" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="E123" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F123" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="E123" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F123" s="2" t="s">
+      <c r="G123" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="G123" s="2" t="s">
+      <c r="H123" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="H123" s="2" t="s">
+      <c r="I123" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="I123" s="2" t="s">
+      <c r="J123" s="2" t="s">
         <v>1095</v>
       </c>
-      <c r="J123" s="2" t="s">
+      <c r="K123" s="2" t="s">
         <v>1096</v>
       </c>
-      <c r="K123" s="2" t="s">
+      <c r="L123" s="2" t="s">
         <v>1097</v>
-      </c>
-      <c r="L123" s="2" t="s">
-        <v>1098</v>
       </c>
       <c r="M123" s="7" t="s">
         <v>28</v>
@@ -16257,29 +16257,29 @@
     </row>
     <row r="124" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>1099</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>1248</v>
-      </c>
-      <c r="C124" s="1" t="s">
+      <c r="D124" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="E124" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F124" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="E124" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F124" s="2" t="s">
+      <c r="G124" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H124" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="G124" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>1103</v>
-      </c>
       <c r="I124" s="2" t="s">
         <v>28</v>
       </c>
@@ -16290,7 +16290,7 @@
         <v>28</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="M124" s="7" t="s">
         <v>28</v>
@@ -16298,40 +16298,40 @@
     </row>
     <row r="125" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="6" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="C125" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="D125" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="D125" s="2" t="s">
+      <c r="E125" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F125" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="E125" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F125" s="2" t="s">
+      <c r="G125" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H125" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="G125" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H125" s="2" t="s">
+      <c r="I125" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J125" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="I125" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J125" s="2" t="s">
-        <v>1110</v>
-      </c>
       <c r="K125" s="2" t="s">
         <v>28</v>
       </c>
       <c r="L125" s="2" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="M125" s="7" t="s">
         <v>28</v>
@@ -16339,73 +16339,73 @@
     </row>
     <row r="126" spans="1:13" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="9" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B126" s="3" t="s">
         <v>1111</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="C126" s="3" t="s">
         <v>1112</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="D126" s="4" t="s">
         <v>1113</v>
       </c>
-      <c r="D126" s="4" t="s">
+      <c r="E126" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F126" s="4" t="s">
         <v>1114</v>
       </c>
-      <c r="E126" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F126" s="4" t="s">
+      <c r="G126" s="4" t="s">
         <v>1115</v>
       </c>
-      <c r="G126" s="4" t="s">
+      <c r="H126" s="4" t="s">
         <v>1116</v>
       </c>
-      <c r="H126" s="4" t="s">
+      <c r="I126" s="4" t="s">
         <v>1117</v>
       </c>
-      <c r="I126" s="4" t="s">
+      <c r="J126" s="4" t="s">
         <v>1118</v>
       </c>
-      <c r="J126" s="4" t="s">
+      <c r="K126" s="4" t="s">
         <v>1119</v>
       </c>
-      <c r="K126" s="4" t="s">
+      <c r="L126" s="4" t="s">
         <v>1120</v>
       </c>
-      <c r="L126" s="4" t="s">
+      <c r="M126" s="10" t="s">
         <v>1121</v>
-      </c>
-      <c r="M126" s="10" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B127" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="C127" s="3" t="s">
         <v>1124</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="D127" s="4" t="s">
         <v>1125</v>
       </c>
-      <c r="D127" s="4" t="s">
+      <c r="E127" s="4" t="s">
         <v>1126</v>
       </c>
-      <c r="E127" s="4" t="s">
+      <c r="F127" s="4" t="s">
         <v>1127</v>
       </c>
-      <c r="F127" s="4" t="s">
+      <c r="G127" s="4" t="s">
         <v>1128</v>
       </c>
-      <c r="G127" s="4" t="s">
+      <c r="H127" s="4" t="s">
         <v>1129</v>
       </c>
-      <c r="H127" s="4" t="s">
+      <c r="I127" s="4" t="s">
         <v>1130</v>
       </c>
-      <c r="I127" s="4" t="s">
-        <v>1131</v>
-      </c>
       <c r="J127" s="4" t="s">
         <v>28</v>
       </c>
@@ -16413,7 +16413,7 @@
         <v>28</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M127" s="10" t="s">
         <v>28</v>
@@ -16421,37 +16421,37 @@
     </row>
     <row r="128" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="9" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="C128" s="3" t="s">
         <v>1133</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="D128" s="4" t="s">
         <v>1134</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="E128" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F128" s="4" t="s">
         <v>1135</v>
       </c>
-      <c r="E128" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F128" s="4" t="s">
+      <c r="G128" s="4" t="s">
         <v>1136</v>
       </c>
-      <c r="G128" s="4" t="s">
+      <c r="H128" s="4" t="s">
         <v>1137</v>
       </c>
-      <c r="H128" s="4" t="s">
+      <c r="I128" s="4" t="s">
         <v>1138</v>
       </c>
-      <c r="I128" s="4" t="s">
+      <c r="J128" s="4" t="s">
         <v>1139</v>
       </c>
-      <c r="J128" s="4" t="s">
+      <c r="K128" s="4" t="s">
         <v>1140</v>
-      </c>
-      <c r="K128" s="4" t="s">
-        <v>1141</v>
       </c>
       <c r="L128" s="4" t="s">
         <v>244</v>
@@ -16462,32 +16462,32 @@
     </row>
     <row r="129" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="9" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>1142</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="C129" s="3" t="s">
         <v>1143</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="D129" s="4" t="s">
         <v>1144</v>
       </c>
-      <c r="D129" s="4" t="s">
+      <c r="E129" s="4" t="s">
         <v>1145</v>
       </c>
-      <c r="E129" s="4" t="s">
+      <c r="F129" s="4" t="s">
         <v>1146</v>
       </c>
-      <c r="F129" s="4" t="s">
+      <c r="G129" s="4" t="s">
         <v>1147</v>
       </c>
-      <c r="G129" s="4" t="s">
+      <c r="H129" s="4" t="s">
         <v>1148</v>
       </c>
-      <c r="H129" s="4" t="s">
+      <c r="I129" s="4" t="s">
         <v>1149</v>
       </c>
-      <c r="I129" s="4" t="s">
-        <v>1150</v>
-      </c>
       <c r="J129" s="4" t="s">
         <v>28</v>
       </c>
@@ -16495,7 +16495,7 @@
         <v>28</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M129" s="10" t="s">
         <v>28</v>
@@ -16503,40 +16503,40 @@
     </row>
     <row r="130" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A130" s="9" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B130" s="3" t="s">
         <v>1151</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="C130" s="3" t="s">
         <v>1152</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="D130" s="4" t="s">
         <v>1153</v>
       </c>
-      <c r="D130" s="4" t="s">
+      <c r="E130" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F130" s="4" t="s">
         <v>1154</v>
       </c>
-      <c r="E130" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F130" s="4" t="s">
+      <c r="G130" s="4" t="s">
         <v>1155</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="H130" s="4" t="s">
         <v>1156</v>
       </c>
-      <c r="H130" s="4" t="s">
+      <c r="I130" s="4" t="s">
         <v>1157</v>
       </c>
-      <c r="I130" s="4" t="s">
+      <c r="J130" s="4" t="s">
         <v>1158</v>
       </c>
-      <c r="J130" s="4" t="s">
+      <c r="K130" s="4" t="s">
         <v>1159</v>
       </c>
-      <c r="K130" s="4" t="s">
+      <c r="L130" s="4" t="s">
         <v>1160</v>
-      </c>
-      <c r="L130" s="4" t="s">
-        <v>1161</v>
       </c>
       <c r="M130" s="10" t="s">
         <v>28</v>
@@ -16544,40 +16544,40 @@
     </row>
     <row r="131" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A131" s="9" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B131" s="3" t="s">
         <v>1162</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="C131" s="3" t="s">
         <v>1163</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="D131" s="4" t="s">
         <v>1164</v>
       </c>
-      <c r="D131" s="4" t="s">
+      <c r="E131" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F131" s="4" t="s">
         <v>1165</v>
       </c>
-      <c r="E131" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F131" s="4" t="s">
+      <c r="G131" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="G131" s="4" t="s">
+      <c r="H131" s="4" t="s">
         <v>1167</v>
       </c>
-      <c r="H131" s="4" t="s">
+      <c r="I131" s="4" t="s">
         <v>1168</v>
       </c>
-      <c r="I131" s="4" t="s">
+      <c r="J131" s="4" t="s">
         <v>1169</v>
       </c>
-      <c r="J131" s="4" t="s">
+      <c r="K131" s="4" t="s">
         <v>1170</v>
       </c>
-      <c r="K131" s="4" t="s">
+      <c r="L131" s="4" t="s">
         <v>1171</v>
-      </c>
-      <c r="L131" s="4" t="s">
-        <v>1172</v>
       </c>
       <c r="M131" s="10" t="s">
         <v>28</v>
@@ -16585,26 +16585,26 @@
     </row>
     <row r="132" spans="1:13" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>1173</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="D132" s="2" t="s">
         <v>1175</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="E132" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F132" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F132" s="2" t="s">
+      <c r="G132" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="G132" s="2" t="s">
-        <v>1178</v>
-      </c>
       <c r="H132" s="2" t="s">
         <v>28</v>
       </c>
@@ -16618,7 +16618,7 @@
         <v>28</v>
       </c>
       <c r="L132" s="2" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="M132" s="7" t="s">
         <v>28</v>
